--- a/tests/fixtures/24_type_tests/24_type_tests_data.xlsx
+++ b/tests/fixtures/24_type_tests/24_type_tests_data.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
   <si>
     <t xml:space="preserve">Type Testing in grepxcel</t>
   </si>
@@ -64,83 +65,101 @@
     <t xml:space="preserve">Numeric:Currency Test</t>
   </si>
   <si>
+    <t xml:space="preserve">Numeric:Number Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String: Text Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is a string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">this is another test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL: URL Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://google.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://example.com/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day-ß</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Äöü-Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decimal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMAGE-网址</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://example.com/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mailto://example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE</t>
+  </si>
+  <si>
     <t xml:space="preserve">€10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric:Number Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String: Text Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is another test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL: URL Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://google.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://example.com/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
@@ -154,8 +173,9 @@
     <numFmt numFmtId="174" formatCode="#,##0.00\ [$USD];[RED]\-#,##0.00\ [$USD]"/>
     <numFmt numFmtId="175" formatCode="#,##0_);\(#,##0\)"/>
     <numFmt numFmtId="176" formatCode="@"/>
+    <numFmt numFmtId="177" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +197,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -221,7 +247,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -286,7 +312,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,6 +347,396 @@
     </dxf>
   </dxfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1366200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1174680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836360" y="2877840"/>
+          <a:ext cx="1366200" cy="1174680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>345600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>342000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="4906080"/>
+          <a:ext cx="345600" cy="342000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>365400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5266080"/>
+          <a:ext cx="365400" cy="360360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>360360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5626080"/>
+          <a:ext cx="548640" cy="360360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>517320</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>360000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 6"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5986080"/>
+          <a:ext cx="517320" cy="360000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1366200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1174680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836360" y="2877840"/>
+          <a:ext cx="1366200" cy="1174680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>345600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>342000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="4906080"/>
+          <a:ext cx="345600" cy="342000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>365400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5266080"/>
+          <a:ext cx="365400" cy="360360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>360360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5626080"/>
+          <a:ext cx="548640" cy="360360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>547920</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>360360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Image 5"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14277960" y="5986080"/>
+          <a:ext cx="547920" cy="360360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -499,7 +919,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.95"/>
@@ -577,7 +997,7 @@
       </c>
       <c r="H3" s="7" t="n">
         <f aca="true">TODAY()</f>
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -704,8 +1124,8 @@
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
+      <c r="B9" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="str">
         <f aca="false">A9</f>
@@ -725,7 +1145,7 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>-10</v>
@@ -749,17 +1169,17 @@
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D11" s="1" t="str">
         <f aca="false">A11</f>
         <v>String: Text Test</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="2" t="str">
         <f aca="false">D11</f>
@@ -773,17 +1193,17 @@
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="D12" s="1" t="str">
         <f aca="false">A12</f>
         <v>URL: URL Test</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="str">
         <f aca="false">D12</f>
@@ -794,9 +1214,9 @@
         <v>http://example.com/2&amp;2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="15"/>
       <c r="G13" s="2"/>
@@ -804,13 +1224,13 @@
     </row>
     <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>25</v>
@@ -839,8 +1259,11 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1</v>
       </c>
@@ -848,36 +1271,133 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="7" t="n">
+        <f aca="false">DATE(1970,2,2)</f>
+        <v>25601</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">D16-D17</f>
+        <v>-1</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1.343433434343</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="14" t="n">
+        <f aca="false">D16+1</f>
+        <v>25602</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <f aca="false">D17-D16</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>4.34E-006</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <f aca="true">D16+RAND()*100</f>
+        <v>25661.7575389431</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <f aca="false">D18-D17</f>
+        <v>59.7575389430858</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(K16:K17)</f>
+        <v>Text 1Text 2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="true">D17+RAND()*1000</f>
+        <v>26344.3113215239</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <f aca="false">D19-D18</f>
+        <v>682.553782580853</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E12" r:id="rId1" display="http://example.com/2"/>
+    <hyperlink ref="L16" r:id="rId2" display="http://example.com/1"/>
+    <hyperlink ref="L17" r:id="rId3" display="http://example.com/1"/>
+    <hyperlink ref="L19" r:id="rId4" display="mailto://example.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -886,5 +1406,550 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.39"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.17"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="98" min="9" style="1" width="10.16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f aca="false">A2</f>
+        <v>Boolean: Bool Test</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="str">
+        <f aca="false">D2</f>
+        <v>Boolean: Bool Test</v>
+      </c>
+      <c r="H2" s="4" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>46085</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f aca="false">A3</f>
+        <v>Date: Day Test</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <f aca="false">B3</f>
+        <v>46085</v>
+      </c>
+      <c r="G3" s="2" t="str">
+        <f aca="false">D3</f>
+        <v>Date: Day Test</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <f aca="true">TODAY()</f>
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f aca="false">A4</f>
+        <v>Date: Duration Test</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <f aca="false">B4</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f aca="false">D4</f>
+        <v>Date: Duration Test</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <f aca="true">TODAY()-(TODAY()-1+TIME(1,1,1))</f>
+        <v>0.957627314814815</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f aca="false">A5</f>
+        <v>Numeric: Decimal Test</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <f aca="false">B5</f>
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <f aca="false">D5</f>
+        <v>Numeric: Decimal Test</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <f aca="false">E5*2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f aca="false">A6</f>
+        <v>Numeric: Float Test</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <f aca="false">B6</f>
+        <v>10.01</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <f aca="false">D6</f>
+        <v>Numeric: Float Test</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <f aca="false">E6*2</f>
+        <v>20.02</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f aca="false">A7</f>
+        <v>Numeric: Integer Test</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <f aca="false">B7</f>
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <f aca="false">D7</f>
+        <v>Numeric: Integer Test</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <f aca="false">E7*2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f aca="false">A8</f>
+        <v>Numeric: Percentage Test</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <f aca="false">B8</f>
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <f aca="false">D8</f>
+        <v>Numeric: Percentage Test</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <f aca="false">E8*2</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f aca="false">A9</f>
+        <v>Numeric:Currency Test</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f aca="false">D9</f>
+        <v>Numeric:Currency Test</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <f aca="false">E9*2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f aca="false">A10</f>
+        <v>Numeric:Number Test</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <f aca="false">B10</f>
+        <v>-10</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <f aca="false">D10</f>
+        <v>Numeric:Number Test</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <f aca="false">E10*2</f>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f aca="false">A11</f>
+        <v>String: Text Test</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <f aca="false">D11</f>
+        <v>String: Text Test</v>
+      </c>
+      <c r="H11" s="2" t="str">
+        <f aca="false">B11&amp;CHAR(10)&amp;E11</f>
+        <v>this is a string
+this is another test</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <f aca="false">A12</f>
+        <v>URL: URL Test</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f aca="false">D12</f>
+        <v>URL: URL Test</v>
+      </c>
+      <c r="H12" s="2" t="str">
+        <f aca="false">E12&amp;"&amp;2"</f>
+        <v>http://example.com/2&amp;2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <f aca="false">DATE(1970,2,2)</f>
+        <v>25601</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">D16-D17</f>
+        <v>-1</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1.343433434343</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <f aca="false">A16+10</f>
+        <v>11</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <f aca="false">D16+1</f>
+        <v>25602</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <f aca="false">D17-D16</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>4.34E-006</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <f aca="false">A17+10</f>
+        <v>21</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <f aca="true">D16+RAND()*100</f>
+        <v>25605.2454237816</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <f aca="false">D18-D17</f>
+        <v>3.2454237816164</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.451065395068077</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <f aca="true">INT(RAND()*100)</f>
+        <v>91</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.499569449098531</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(K16:K17)</f>
+        <v>Text 1Text 2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <f aca="false">A18+10</f>
+        <v>31</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="true">D17+RAND()*1000</f>
+        <v>26106.3376847216</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <f aca="false">D19-D18</f>
+        <v>501.09226093996</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <f aca="true">INT(RAND()*100)</f>
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <f aca="true">RAND()</f>
+        <v>0.943309375958181</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <f aca="true">INT(RAND()*100)</f>
+        <v>63</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <f aca="true">RAND()-1</f>
+        <v>-0.0656315944407188</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <f aca="false">A19+10</f>
+        <v>41</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <f aca="false">A20+10</f>
+        <v>51</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E12" r:id="rId1" display="http://example.com/2"/>
+    <hyperlink ref="L16" r:id="rId2" display="http://example.com/1"/>
+    <hyperlink ref="L17" r:id="rId3" display="http://example.com/1"/>
+    <hyperlink ref="L19" r:id="rId4" display="mailto://example.com"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/tests/fixtures/24_type_tests/24_type_tests_data.xlsx
+++ b/tests/fixtures/24_type_tests/24_type_tests_data.xlsx
@@ -1,18 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/14e38b7f4ac4520e/2026/grepxcel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_E70CEB606E77A57DF8B6053EBF59DFA17740465F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B1B7CF7-3553-40B4-BFBF-BE5C94DA94E5}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1_2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -20,183 +36,207 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="3">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="3">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
   <si>
-    <t xml:space="preserve">Type Testing in grepxcel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not Formatted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formatted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNCTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean: Bool Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date: Day Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date: Duration Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric: Decimal Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric: Float Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric: Integer Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric: Percentage Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric:Currency Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numeric:Number Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String: Text Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is a string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">this is another test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL: URL Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://google.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://example.com/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boolean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day-ß</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Äöü-Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMAGE-网址</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://example.com/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mailto://example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€10</t>
+    <t>Type Testing in grepxcel</t>
+  </si>
+  <si>
+    <t>Not Formatted</t>
+  </si>
+  <si>
+    <t>Formatted</t>
+  </si>
+  <si>
+    <t>FUNCTION</t>
+  </si>
+  <si>
+    <t>Boolean: Bool Test</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Date: Day Test</t>
+  </si>
+  <si>
+    <t>Date: Duration Test</t>
+  </si>
+  <si>
+    <t>Numeric: Decimal Test</t>
+  </si>
+  <si>
+    <t>Numeric: Float Test</t>
+  </si>
+  <si>
+    <t>Numeric: Integer Test</t>
+  </si>
+  <si>
+    <t>Numeric: Percentage Test</t>
+  </si>
+  <si>
+    <t>Numeric:Currency Test</t>
+  </si>
+  <si>
+    <t>Numeric:Number Test</t>
+  </si>
+  <si>
+    <t>String: Text Test</t>
+  </si>
+  <si>
+    <t>this is a string</t>
+  </si>
+  <si>
+    <t>this is another test</t>
+  </si>
+  <si>
+    <t>URL: URL Test</t>
+  </si>
+  <si>
+    <t>http://google.com</t>
+  </si>
+  <si>
+    <t>http://example.com/2</t>
+  </si>
+  <si>
+    <t>Image Test</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Day-ß</t>
+  </si>
+  <si>
+    <t>Äöü-Duration</t>
+  </si>
+  <si>
+    <t>Decimal</t>
+  </si>
+  <si>
+    <t>Float</t>
+  </si>
+  <si>
+    <t>Integer</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>IMAGE-网址</t>
+  </si>
+  <si>
+    <t>Text 1</t>
+  </si>
+  <si>
+    <t>http://example.com/1</t>
+  </si>
+  <si>
+    <t>Text 2</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>mailto://example.com</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>€10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="QQ\ yy"/>
-    <numFmt numFmtId="168" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="169" formatCode="[hh]:mm:ss"/>
-    <numFmt numFmtId="170" formatCode="[hh]:mm:ss.00"/>
-    <numFmt numFmtId="171" formatCode="0.00E+000"/>
-    <numFmt numFmtId="172" formatCode="[$-409]0"/>
-    <numFmt numFmtId="173" formatCode="0.00%"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00\ [$USD];[RED]\-#,##0.00\ [$USD]"/>
-    <numFmt numFmtId="175" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="176" formatCode="@"/>
-    <numFmt numFmtId="177" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="11">
+    <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="\Q\Q\ yy"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="168" formatCode="[hh]:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="[hh]:mm:ss.00"/>
+    <numFmt numFmtId="170" formatCode="0.00E+000"/>
+    <numFmt numFmtId="171" formatCode="[$-409]0"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00\ [$USD];[Red]\-#,##0.00\ [$USD]"/>
+    <numFmt numFmtId="173" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="174" formatCode="mmmm\ d&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -214,7 +254,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -222,135 +262,75 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -366,11 +346,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1"/>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -404,11 +390,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 2"/>
+        <xdr:cNvPr id="3" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -442,11 +434,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 3"/>
+        <xdr:cNvPr id="4" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -480,11 +478,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 4"/>
+        <xdr:cNvPr id="5" name="Image 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -518,11 +522,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 6"/>
+        <xdr:cNvPr id="6" name="Image 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -545,7 +555,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -554,18 +564,24 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1366200</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>42</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>1174680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 1"/>
+        <xdr:cNvPr id="6" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -599,11 +615,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 2"/>
+        <xdr:cNvPr id="7" name="Image 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -637,11 +659,17 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 3"/>
+        <xdr:cNvPr id="8" name="Image 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -670,16 +698,22 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>360360</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1132</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 4"/>
+        <xdr:cNvPr id="9" name="Image 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -708,16 +742,22 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>547920</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>360360</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1131</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 5"/>
+        <xdr:cNvPr id="10" name="Image 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
@@ -739,8 +779,88 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+    <v>Engineer programming robot in robotics research facility</v>
+  </rv>
+  <rv s="1">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="1">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+</richValueRels>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -782,12 +902,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -816,7 +936,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -837,7 +957,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -888,7 +1008,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -906,34 +1026,33 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.17"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="10.16"/>
+    <col min="1" max="1" width="22.921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.07421875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" style="1"/>
+    <col min="4" max="4" width="22.921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3828125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.15234375" style="1"/>
+    <col min="7" max="7" width="22.921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.15234375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,14 +1065,14 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -961,213 +1080,213 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f aca="false">A2</f>
+        <f t="shared" ref="D2:D12" si="0">A2</f>
         <v>Boolean: Bool Test</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <f aca="false">D2</f>
+      <c r="G2" s="1" t="str">
+        <f t="shared" ref="G2:G12" si="1">D2</f>
         <v>Boolean: Bool Test</v>
       </c>
-      <c r="H2" s="4" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="H2" s="1" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="3">
         <v>46085</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f aca="false">A3</f>
+        <f t="shared" si="0"/>
         <v>Date: Day Test</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <f aca="false">B3</f>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E8" si="2">B3</f>
         <v>46085</v>
       </c>
-      <c r="G3" s="2" t="str">
-        <f aca="false">D3</f>
+      <c r="G3" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Date: Day Test</v>
       </c>
-      <c r="H3" s="7" t="n">
-        <f aca="true">TODAY()</f>
+      <c r="H3" s="5">
+        <f ca="1">TODAY()</f>
         <v>46287</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f aca="false">A4</f>
+        <f t="shared" si="0"/>
         <v>Date: Duration Test</v>
       </c>
-      <c r="E4" s="9" t="n">
-        <f aca="false">B4</f>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="str">
-        <f aca="false">D4</f>
+      <c r="G4" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Date: Duration Test</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <f aca="true">TODAY()-(TODAY()-1+TIME(1,1,1))</f>
-        <v>0.957627314814815</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="6">
+        <f ca="1">TODAY()-(TODAY()-1+TIME(1,1,1))</f>
+        <v>0.95762731481227092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f aca="false">A5</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Decimal Test</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <f aca="false">B5</f>
+      <c r="E5" s="1">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="str">
-        <f aca="false">D5</f>
+      <c r="G5" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Decimal Test</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <f aca="false">E5*2</f>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H10" si="3">E5*2</f>
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="1">
         <v>10.01</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f aca="false">A6</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Float Test</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <f aca="false">B6</f>
+      <c r="E6" s="8">
+        <f t="shared" si="2"/>
         <v>10.01</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <f aca="false">D6</f>
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Float Test</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <f aca="false">E6*2</f>
+      <c r="H6" s="1">
+        <f t="shared" si="3"/>
         <v>20.02</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f aca="false">A7</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Integer Test</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">B7</f>
+      <c r="E7" s="9">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <f aca="false">D7</f>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Integer Test</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <f aca="false">E7*2</f>
+      <c r="H7" s="1">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10">
         <v>0.1</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f aca="false">A8</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Percentage Test</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <f aca="false">B8</f>
+      <c r="E8" s="10">
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <f aca="false">D8</f>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Percentage Test</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <f aca="false">E8*2</f>
+      <c r="H8" s="1">
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="1">
         <v>10</v>
       </c>
       <c r="D9" s="1" t="str">
-        <f aca="false">A9</f>
+        <f t="shared" si="0"/>
         <v>Numeric:Currency Test</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="11">
         <v>10</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <f aca="false">D9</f>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric:Currency Test</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <f aca="false">E9*2</f>
+      <c r="H9" s="1">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="1">
         <v>-10</v>
       </c>
       <c r="D10" s="1" t="str">
-        <f aca="false">A10</f>
+        <f t="shared" si="0"/>
         <v>Numeric:Number Test</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">B10</f>
+      <c r="E10" s="12">
+        <f>B10</f>
         <v>-10</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <f aca="false">D10</f>
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric:Number Test</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <f aca="false">E10*2</f>
+      <c r="H10" s="1">
+        <f t="shared" si="3"/>
         <v>-20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1175,54 +1294,52 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="str">
-        <f aca="false">A11</f>
+        <f t="shared" si="0"/>
         <v>String: Text Test</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="2" t="str">
-        <f aca="false">D11</f>
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>String: Text Test</v>
       </c>
-      <c r="H11" s="2" t="str">
-        <f aca="false">B11&amp;CHAR(10)&amp;E11</f>
+      <c r="H11" s="1" t="str">
+        <f>B11&amp;CHAR(10)&amp;E11</f>
         <v>this is a string
 this is another test</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f aca="false">A12</f>
+        <f t="shared" si="0"/>
         <v>URL: URL Test</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <f aca="false">D12</f>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>URL: URL Test</v>
       </c>
-      <c r="H12" s="2" t="str">
-        <f aca="false">E12&amp;"&amp;2"</f>
+      <c r="H12" s="1" t="str">
+        <f>E12&amp;"&amp;2"</f>
         <v>http://example.com/2&amp;2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="113.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="13"/>
+    </row>
+    <row r="15" spans="1:13" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1259,39 +1376,39 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="B16" s="1" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <f aca="false">DATE(1970,2,2)</f>
+      <c r="D16" s="5">
+        <f>DATE(1970,2,2)</f>
         <v>25601</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">D16-D17</f>
+      <c r="E16" s="12">
+        <f>D16-D17</f>
         <v>-1</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="1">
         <v>4</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>1.343433434343</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="G16" s="1">
+        <v>1.3434334343430001</v>
+      </c>
+      <c r="H16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="10">
         <v>0.05</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="11">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1301,32 +1418,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="n">
-        <f aca="false">FALSE()</f>
+    <row r="17" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="1" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">D16+1</f>
+      <c r="D17" s="12">
+        <f>D16+1</f>
         <v>25602</v>
       </c>
-      <c r="E17" s="14" t="n">
-        <f aca="false">D17-D16</f>
+      <c r="E17" s="12">
+        <f>D17-D16</f>
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="1">
         <v>5</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>4.34E-006</v>
-      </c>
-      <c r="H17" s="1" t="n">
+      <c r="G17" s="1">
+        <v>4.34E-6</v>
+      </c>
+      <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>0.6</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="1">
         <v>2</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1336,100 +1453,95 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+    <row r="18" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <f aca="true">D16+RAND()*100</f>
-        <v>25661.7575389431</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <f aca="false">D18-D17</f>
-        <v>59.7575389430858</v>
-      </c>
-      <c r="F18" s="1" t="n">
+      <c r="D18" s="5">
+        <f ca="1">D16+RAND()*100</f>
+        <v>25646.186719645699</v>
+      </c>
+      <c r="E18" s="12">
+        <f ca="1">D18-D17</f>
+        <v>44.186719645698759</v>
+      </c>
+      <c r="F18" s="1">
         <v>6</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="1">
         <v>3</v>
       </c>
       <c r="K18" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT(K16:K17)</f>
+        <f>_xlfn.CONCAT(K16:K17)</f>
         <v>Text 1Text 2</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="17" t="n">
-        <f aca="true">D17+RAND()*1000</f>
-        <v>26344.3113215239</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <f aca="false">D19-D18</f>
-        <v>682.553782580853</v>
-      </c>
-      <c r="J19" s="1" t="n">
+      <c r="D19" s="15">
+        <f ca="1">D17+RAND()*1000</f>
+        <v>26451.044091649448</v>
+      </c>
+      <c r="E19" s="12">
+        <f ca="1">D19-D18</f>
+        <v>804.85737200374933</v>
+      </c>
+      <c r="J19" s="1">
         <v>4</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="15" t="s">
+    <row r="20" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="13" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15" t="s">
+      <c r="M20" s="1" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="2:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E12" r:id="rId1" display="http://example.com/2"/>
-    <hyperlink ref="L16" r:id="rId2" display="http://example.com/1"/>
-    <hyperlink ref="L17" r:id="rId3" display="http://example.com/1"/>
-    <hyperlink ref="L19" r:id="rId4" display="mailto://example.com"/>
+    <hyperlink ref="E12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L16" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L19" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:CT25"/>
+  <sheetFormatPr defaultColWidth="10.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.17"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="98" min="9" style="1" width="10.16"/>
+    <col min="1" max="1" width="22.921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.07421875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.15234375" style="1"/>
+    <col min="4" max="4" width="22.921875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3828125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.15234375" style="1"/>
+    <col min="7" max="7" width="22.921875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.15234375" style="1" customWidth="1"/>
+    <col min="9" max="98" width="10.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1442,14 +1554,14 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1457,166 +1569,166 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="str">
-        <f aca="false">A2</f>
+        <f t="shared" ref="D2:D12" si="0">A2</f>
         <v>Boolean: Bool Test</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <f aca="false">D2</f>
+      <c r="G2" s="1" t="str">
+        <f t="shared" ref="G2:G13" si="1">D2</f>
         <v>Boolean: Bool Test</v>
       </c>
-      <c r="H2" s="4" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="H2" s="1" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="3">
         <v>46085</v>
       </c>
       <c r="D3" s="1" t="str">
-        <f aca="false">A3</f>
+        <f t="shared" si="0"/>
         <v>Date: Day Test</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <f aca="false">B3</f>
+      <c r="E3" s="4">
+        <f t="shared" ref="E3:E8" si="2">B3</f>
         <v>46085</v>
       </c>
-      <c r="G3" s="2" t="str">
-        <f aca="false">D3</f>
+      <c r="G3" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Date: Day Test</v>
       </c>
-      <c r="H3" s="7" t="n">
-        <f aca="true">TODAY()</f>
+      <c r="H3" s="5">
+        <f ca="1">TODAY()</f>
         <v>46287</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="str">
-        <f aca="false">A4</f>
+        <f t="shared" si="0"/>
         <v>Date: Duration Test</v>
       </c>
-      <c r="E4" s="9" t="n">
-        <f aca="false">B4</f>
+      <c r="E4" s="7">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="str">
-        <f aca="false">D4</f>
+      <c r="G4" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Date: Duration Test</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <f aca="true">TODAY()-(TODAY()-1+TIME(1,1,1))</f>
-        <v>0.957627314814815</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="6">
+        <f ca="1">TODAY()-(TODAY()-1+TIME(1,1,1))</f>
+        <v>0.95762731481227092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f aca="false">A5</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Decimal Test</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <f aca="false">B5</f>
+      <c r="E5" s="1">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="str">
-        <f aca="false">D5</f>
+      <c r="G5" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Decimal Test</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <f aca="false">E5*2</f>
+      <c r="H5" s="1">
+        <f t="shared" ref="H5:H10" si="3">E5*2</f>
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="1">
         <v>10.01</v>
       </c>
       <c r="D6" s="1" t="str">
-        <f aca="false">A6</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Float Test</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <f aca="false">B6</f>
+      <c r="E6" s="8">
+        <f t="shared" si="2"/>
         <v>10.01</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <f aca="false">D6</f>
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Float Test</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <f aca="false">E6*2</f>
+      <c r="H6" s="1">
+        <f t="shared" si="3"/>
         <v>20.02</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="str">
-        <f aca="false">A7</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Integer Test</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">B7</f>
+      <c r="E7" s="9">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <f aca="false">D7</f>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Integer Test</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <f aca="false">E7*2</f>
+      <c r="H7" s="1">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="10">
         <v>0.1</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f aca="false">A8</f>
+        <f t="shared" si="0"/>
         <v>Numeric: Percentage Test</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <f aca="false">B8</f>
+      <c r="E8" s="10">
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <f aca="false">D8</f>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric: Percentage Test</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <f aca="false">E8*2</f>
+      <c r="H8" s="1">
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1624,46 +1736,46 @@
         <v>43</v>
       </c>
       <c r="D9" s="1" t="str">
-        <f aca="false">A9</f>
+        <f t="shared" si="0"/>
         <v>Numeric:Currency Test</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="11">
         <v>10</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <f aca="false">D9</f>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric:Currency Test</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <f aca="false">E9*2</f>
+      <c r="H9" s="1">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="1">
         <v>-10</v>
       </c>
       <c r="D10" s="1" t="str">
-        <f aca="false">A10</f>
+        <f t="shared" si="0"/>
         <v>Numeric:Number Test</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <f aca="false">B10</f>
+      <c r="E10" s="12">
+        <f>B10</f>
         <v>-10</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <f aca="false">D10</f>
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>Numeric:Number Test</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <f aca="false">E10*2</f>
+      <c r="H10" s="1">
+        <f t="shared" si="3"/>
         <v>-20</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1671,54 +1783,65 @@
         <v>16</v>
       </c>
       <c r="D11" s="1" t="str">
-        <f aca="false">A11</f>
+        <f t="shared" si="0"/>
         <v>String: Text Test</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="2" t="str">
-        <f aca="false">D11</f>
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>String: Text Test</v>
       </c>
-      <c r="H11" s="2" t="str">
-        <f aca="false">B11&amp;CHAR(10)&amp;E11</f>
+      <c r="H11" s="1" t="str">
+        <f>B11&amp;CHAR(10)&amp;E11</f>
         <v>this is a string
 this is another test</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f aca="false">A12</f>
+        <f t="shared" si="0"/>
         <v>URL: URL Test</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <f aca="false">D12</f>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="1"/>
         <v>URL: URL Test</v>
       </c>
-      <c r="H12" s="2" t="str">
-        <f aca="false">E12&amp;"&amp;2"</f>
+      <c r="H12" s="1" t="str">
+        <f>E12&amp;"&amp;2"</f>
         <v>http://example.com/2&amp;2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="113.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:13" ht="113.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="1" t="str">
+        <f>A13</f>
+        <v>Image Test</v>
+      </c>
+      <c r="E13" s="13" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Image Test</v>
+      </c>
+      <c r="H13" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="26.15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1755,39 +1878,39 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:13" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="b">
-        <f aca="false">TRUE()</f>
+      <c r="B16" s="1" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <f aca="false">DATE(1970,2,2)</f>
+      <c r="D16" s="5">
+        <f>DATE(1970,2,2)</f>
         <v>25601</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <f aca="false">D16-D17</f>
+      <c r="E16" s="12">
+        <f>D16-D17</f>
         <v>-1</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="1">
         <v>4</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>1.343433434343</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="G16" s="1">
+        <v>1.3434334343430001</v>
+      </c>
+      <c r="H16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="I16" s="10">
         <v>0.05</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="11">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1797,36 +1920,36 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <f aca="false">A16+10</f>
+    <row r="17" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <f>A16+10</f>
         <v>11</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <f aca="false">FALSE()</f>
+      <c r="B17" s="1" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">D16+1</f>
+      <c r="D17" s="12">
+        <f>D16+1</f>
         <v>25602</v>
       </c>
-      <c r="E17" s="14" t="n">
-        <f aca="false">D17-D16</f>
+      <c r="E17" s="12">
+        <f>D17-D16</f>
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="1">
         <v>5</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>4.34E-006</v>
-      </c>
-      <c r="H17" s="1" t="n">
+      <c r="G17" s="1">
+        <v>4.34E-6</v>
+      </c>
+      <c r="H17" s="1">
         <v>1</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>0.6</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="1">
         <v>2</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1836,120 +1959,115 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
-        <f aca="false">A17+10</f>
+    <row r="18" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="1">
+        <f>A17+10</f>
         <v>21</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="7" t="n">
-        <f aca="true">D16+RAND()*100</f>
-        <v>25605.2454237816</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <f aca="false">D18-D17</f>
-        <v>3.2454237816164</v>
-      </c>
-      <c r="F18" s="1" t="n">
+      <c r="D18" s="5">
+        <f ca="1">D16+RAND()*100</f>
+        <v>25662.803625532011</v>
+      </c>
+      <c r="E18" s="12">
+        <f ca="1">D18-D17</f>
+        <v>60.80362553201121</v>
+      </c>
+      <c r="F18" s="1">
         <v>6</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.451065395068077</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <f aca="true">INT(RAND()*100)</f>
-        <v>91</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.499569449098531</v>
-      </c>
-      <c r="J18" s="1" t="n">
+      <c r="G18" s="1">
+        <f ca="1">RAND()</f>
+        <v>0.63033136525345068</v>
+      </c>
+      <c r="H18" s="1">
+        <f ca="1">INT(RAND()*100)</f>
+        <v>14</v>
+      </c>
+      <c r="I18" s="1">
+        <f ca="1">RAND()</f>
+        <v>0.26761889841154496</v>
+      </c>
+      <c r="J18" s="1">
         <v>3</v>
       </c>
       <c r="K18" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT(K16:K17)</f>
+        <f>_xlfn.CONCAT(K16:K17)</f>
         <v>Text 1Text 2</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
-        <f aca="false">A18+10</f>
+    <row r="19" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="1">
+        <f>A18+10</f>
         <v>31</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="17" t="n">
-        <f aca="true">D17+RAND()*1000</f>
-        <v>26106.3376847216</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <f aca="false">D19-D18</f>
-        <v>501.09226093996</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <f aca="true">INT(RAND()*100)</f>
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <f aca="true">RAND()</f>
-        <v>0.943309375958181</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <f aca="true">INT(RAND()*100)</f>
-        <v>63</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <f aca="true">RAND()-1</f>
-        <v>-0.0656315944407188</v>
-      </c>
-      <c r="J19" s="1" t="n">
+      <c r="D19" s="15">
+        <f ca="1">D17+RAND()*1000</f>
+        <v>25658.723432807768</v>
+      </c>
+      <c r="E19" s="12">
+        <f ca="1">D19-D18</f>
+        <v>-4.0801927242428064</v>
+      </c>
+      <c r="F19" s="1">
+        <f ca="1">INT(RAND()*100)</f>
+        <v>53</v>
+      </c>
+      <c r="G19" s="1">
+        <f ca="1">RAND()</f>
+        <v>3.6988001088220535E-2</v>
+      </c>
+      <c r="H19" s="1">
+        <f ca="1">INT(RAND()*100)</f>
+        <v>95</v>
+      </c>
+      <c r="I19" s="10">
+        <f ca="1">RAND()-1</f>
+        <v>-0.15940971326972786</v>
+      </c>
+      <c r="J19" s="1">
         <v>4</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
-        <f aca="false">A19+10</f>
+    <row r="20" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <f>A19+10</f>
         <v>41</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
-        <f aca="false">A20+10</f>
+    <row r="21" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <f>A20+10</f>
         <v>51</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="1:12" ht="28.4" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E12" r:id="rId1" display="http://example.com/2"/>
-    <hyperlink ref="L16" r:id="rId2" display="http://example.com/1"/>
-    <hyperlink ref="L17" r:id="rId3" display="http://example.com/1"/>
-    <hyperlink ref="L19" r:id="rId4" display="mailto://example.com"/>
+    <hyperlink ref="E12" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L16" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L17" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="L19" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId5"/>
 </worksheet>
 </file>